--- a/dados/[B3] Contagem direta de ocupacao/B3_contagem_sorteio_visitas.xlsx
+++ b/dados/[B3] Contagem direta de ocupacao/B3_contagem_sorteio_visitas.xlsx
@@ -542,7 +542,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sorteio das visitas da contagem direta de ocupação (Bloco D)</t>
+          <t>Sorteio das visitas da contagem direta de ocupação (Bloco B3)</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>• Os números aleatórios foram gerados com semente fixa (20260916) pelo script _src/[D] Contagem direta de ocupacao/build_contagem_sorteio.py e não devem ser editados.</t>
+          <t>• Os números aleatórios foram gerados com semente fixa (20260916) pelo script _src/[B3] Contagem direta de ocupacao/build/B3-b_contagem_sorteio.py e não devem ser editados.</t>
         </is>
       </c>
     </row>

--- a/dados/[B3] Contagem direta de ocupacao/B3_contagem_sorteio_visitas.xlsx
+++ b/dados/[B3] Contagem direta de ocupacao/B3_contagem_sorteio_visitas.xlsx
@@ -646,7 +646,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>• Os números aleatórios foram gerados com semente fixa (20260916) pelo script _src/[B3] Contagem direta de ocupacao/build/B3-b_contagem_sorteio.py e não devem ser editados.</t>
+          <t>• Os números aleatórios foram gerados com semente fixa (20260916) pelo script _src/[B3] Contagem direta de ocupacao/Contagem direta/build/B3-b_contagem_sorteio.py e não devem ser editados.</t>
         </is>
       </c>
     </row>
